--- a/data/trans_dic/P79$impuestos_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P79$impuestos_2023-Clase-trans_dic.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,65</t>
+          <t>0,13; 1,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,95</t>
+          <t>0,18; 2,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,28</t>
+          <t>0,25; 1,26</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,43</t>
+          <t>0,17; 1,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,77</t>
+          <t>0,93; 3,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,21</t>
+          <t>0,33; 3,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,49</t>
+          <t>0,97; 3,18</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,64</t>
+          <t>0,87; 2,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,59</t>
+          <t>0,52; 1,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,9</t>
+          <t>0,9; 2,01</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,98</t>
+          <t>1,04; 3,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,83</t>
+          <t>1,39; 3,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,8</t>
+          <t>1,53; 2,94</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,3</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,47</t>
+          <t>0,69; 2,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,32</t>
+          <t>0,76; 2,47</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,74</t>
+          <t>0,98; 1,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,51</t>
+          <t>0,97; 1,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,48</t>
+          <t>1,06; 1,59</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6418</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>660; 8254</t>
+          <t>721; 7772</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>892; 8564</t>
+          <t>874; 9711</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2533; 12036</t>
+          <t>2537; 12906</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3947</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6312</t>
+          <t>0; 6238</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>656; 5399</t>
+          <t>691; 5612</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1337; 8729</t>
+          <t>1422; 9509</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>11428</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1254; 18184</t>
+          <t>4286; 16482</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>555; 5295</t>
+          <t>620; 6470</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4023; 20500</t>
+          <t>6249; 20557</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24610</t>
+          <t>26008</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9674; 26800</t>
+          <t>9634; 27945</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3254; 15117</t>
+          <t>4304; 15013</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16054; 37274</t>
+          <t>17426; 38969</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>16605</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23687</t>
+          <t>27642</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4542; 18037</t>
+          <t>5571; 21137</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8640; 20992</t>
+          <t>11075; 24401</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16014; 33543</t>
+          <t>20408; 39127</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>13169</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 11343</t>
+          <t>0; 13177</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5348; 17725</t>
+          <t>5535; 19526</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6016; 21636</t>
+          <t>7680; 24964</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>41808</t>
+          <t>44895</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>39121</t>
+          <t>43718</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>80929</t>
+          <t>88613</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>29128; 57159</t>
+          <t>32820; 61086</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28697; 51066</t>
+          <t>34013; 57614</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>63316; 98965</t>
+          <t>72581; 108747</t>
         </is>
       </c>
     </row>
